--- a/Extra/testcase.xlsx
+++ b/Extra/testcase.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hoctap\Lập Trình Mạng\Ung-Dung-ChatTCP\Extra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2942CA2D-1481-459C-BA4F-0CB75039031F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F153401C-0A61-4EC2-BD69-3520C266BAC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="120">
   <si>
     <t>STT(Mã TC)</t>
   </si>
@@ -35,9 +48,6 @@
   </si>
   <si>
     <t>Kết quả mong đợi(Expected result)</t>
-  </si>
-  <si>
-    <t>Kết quả thực tế(Actual Result)</t>
   </si>
   <si>
     <t>Trạng thái(Status)</t>
@@ -63,9 +73,6 @@
 2. Client kết nối thành công </t>
   </si>
   <si>
-    <t>Khi cho chạy Server và Client song song thì đổi địa chỉ Port sang thành chữ thì vẫn có thể đăng nhập vô, nhưng khi tắt Server thì Client chỉ nhận Port:5000</t>
-  </si>
-  <si>
     <t>TC_02</t>
   </si>
   <si>
@@ -85,10 +92,6 @@
 - Hiện thông báo lỗi text:”Khônng thể kết nối đến Server, vui long kiểm tra lại Port.”</t>
   </si>
   <si>
-    <t>- Client chạy  song song Server thì Port chỉ nhận số 5000, còn chữ thì có thể vô được Client ví dụ:a, abcds.
-- Khi đóng Server thì Port chỉ nhận số 5000, nếu không phải số 5000 thì sẽ hiện “không thể kết nối đến Server…”</t>
-  </si>
-  <si>
     <t>TC_03</t>
   </si>
   <si>
@@ -102,11 +105,6 @@
     <t>Text:”Chào mọi người, buổi sáng tốt lành”</t>
   </si>
   <si>
-    <t xml:space="preserve">- Màn hình Client A hiện tin nhắn.
-- Màn hình Client B nhận và hiện : admin:”Chào mọi người, buổi sáng tốt lành”
-- </t>
-  </si>
-  <si>
     <t>Client A tên là admin, Client B tên là Thiên Phước.
 - Admin gửi tin nhắn cho Thiên Phước thì có hiện tin nhắn admin đã gửi</t>
   </si>
@@ -164,29 +162,273 @@
     <t>TC_07</t>
   </si>
   <si>
-    <t>Thu hồi tin nhắn, hình ảnh</t>
-  </si>
-  <si>
-    <t>1. Client có thể thu hồi tin nhắn</t>
-  </si>
-  <si>
-    <t>Text: nhấn vào tin nhắn hay ảnh để thu hồi</t>
-  </si>
-  <si>
-    <t>- Client có thể thu hồi tin nhắn, đồng thời hiện lên dòng thông báo:” tin nhán/ảnh đã bị thu hồi”</t>
-  </si>
-  <si>
     <t>TC_08</t>
   </si>
   <si>
     <t>Xử lý khi Client ngắt kết nối đột ngột</t>
+  </si>
+  <si>
+    <t>Test1</t>
+  </si>
+  <si>
+    <t>Test2</t>
+  </si>
+  <si>
+    <t>Test 3</t>
+  </si>
+  <si>
+    <t>Proof</t>
+  </si>
+  <si>
+    <t>Cho Client và Server chạy song, nhập địa chỉ IP là 127.0.0.1 và Port là 5000 thì Client kết nối thành công</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>ImageTC-01
+Kết quả ImageTC-01</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client chạy  song song Server thì Port chỉ nhận số 5000, nếu không phải Port 5000 thì sẽ hiện thông báo:"không thể kết nối với Server, nhưng khi nhập chữ bất kì thì có thể vô được Client ví dụ:a, abcds.
+</t>
+  </si>
+  <si>
+    <t>ImageTC-02
+Kết quả ImageTC-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Màn hình Client A gửi tin nhắn.
+Màn hình Client B nhận và hiện : admin:”Chào mọi người, buổi sáng tốt lành”</t>
+  </si>
+  <si>
+    <t>Kết quả ImageTC-03.jpg</t>
+  </si>
+  <si>
+    <t>Kết quả ImageTC-05.jpg</t>
+  </si>
+  <si>
+    <t>Kết quả ImageTC-06.jpg</t>
+  </si>
+  <si>
+    <t>Kết quả ImageTC-07.jpg</t>
+  </si>
+  <si>
+    <t>TC_09</t>
+  </si>
+  <si>
+    <t>Chức năng cập nhật hồ sơ, Avatar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Có thể thay đổi tên hiển thị, thay đổi Avatar </t>
+  </si>
+  <si>
+    <t>Thay đổi tên hiển thị và Avatar</t>
+  </si>
+  <si>
+    <t>Tẳt Client một cách đột ngột</t>
+  </si>
+  <si>
+    <t>Thay tên hiển thị thành Phước, cập nhật Avartar Mads Mikkelsen sau đó nhấn lưu</t>
+  </si>
+  <si>
+    <t>Nhấn vào dấu X để tắt Client</t>
+  </si>
+  <si>
+    <t>ImageTC-09
+Kết quả ImageTC-09</t>
+  </si>
+  <si>
+    <t>TC_10</t>
+  </si>
+  <si>
+    <t>Tải lại lịch sử chat</t>
+  </si>
+  <si>
+    <t>Nhấn vào tài khoản để tải lại lịch sử</t>
+  </si>
+  <si>
+    <t>Tải lại lịch sử đã bị ẩn trước đó</t>
+  </si>
+  <si>
+    <t>Do là vẫn hiển hị tin nhắn nên không thể xác minh</t>
+  </si>
+  <si>
+    <t>TC_11</t>
+  </si>
+  <si>
+    <t>Đổi mật khẩu</t>
+  </si>
+  <si>
+    <t>Nhấn vào tài khoản để đổi mật khẩu</t>
+  </si>
+  <si>
+    <t>Xác minh mật khẩu cũ rồi đổi sang mật khẩu mới, ví dụ đổi ThienPhuoc20 sang ThienPhuoc123</t>
+  </si>
+  <si>
+    <t>Đổi mật khẩu thành công</t>
+  </si>
+  <si>
+    <t>Kết quả ImageTC-11.jpg</t>
+  </si>
+  <si>
+    <t>TC_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhấn vào chữ Admin trong tài khoản quản trị viên </t>
+  </si>
+  <si>
+    <t>Xem danh sách User và khóa khả năng hoạt động của User</t>
+  </si>
+  <si>
+    <t>Hiển thị ra danh sách User,tên hiển thị, vai trò, trạng thái, hoạt động</t>
+  </si>
+  <si>
+    <t>Đúng như mong đợi và Admin có thể khóa tài khoản của User</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ImageTC-12
+Kết quả ImageTC-12
+</t>
+  </si>
+  <si>
+    <t>TC_13</t>
+  </si>
+  <si>
+    <t>Trích dẫn tin nhắn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chọn tin nhắn muốn trích dẫn rồi sau đó nhấn vào ô trích dẫn </t>
+  </si>
+  <si>
+    <t>Chọn tin nhắn "chào mọi người, buổi sáng tốt lành</t>
+  </si>
+  <si>
+    <t>Client Phước cảm ơn tin nhắn chào buổi sáng của Client Admin</t>
+  </si>
+  <si>
+    <t>Client Admin nhận được tin nhắn cảm ơn trích dẫn theo lời chào cảm ơn của mình</t>
+  </si>
+  <si>
+    <t>Kết quả ImageTC-13.jpg</t>
+  </si>
+  <si>
+    <t>TC_14</t>
+  </si>
+  <si>
+    <t>Chức năng gửi video và file</t>
+  </si>
+  <si>
+    <t>Client Admin có thể chọn video muốn gửi trong ô Video và gửi file trong Ô file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chọn một video để gửi và gửi file extra </t>
+  </si>
+  <si>
+    <t>Nhận được video và file, có thể mở lên xem được</t>
+  </si>
+  <si>
+    <t>Kết quả ImageTC-14.jpg</t>
+  </si>
+  <si>
+    <t>TC_15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chức năng gửi </t>
+  </si>
+  <si>
+    <t>Không cần nhấn Enter để gửi tin nhắn</t>
+  </si>
+  <si>
+    <t>Nhắn "sáng rồi dậy đi" rồi nhấn vào ô Gửi</t>
+  </si>
+  <si>
+    <t>Nhận được tin nhắn</t>
+  </si>
+  <si>
+    <t>Thu hồi tin nhắn, hình ảnh, video và file</t>
+  </si>
+  <si>
+    <t>Text: nhấn vào tin nhắn hay ảnh, video hoặc file để thu hồi</t>
+  </si>
+  <si>
+    <t>Client có thể thu hồi tin nhắn/ảnh/video/file, đồng thời hiện lên dòng thông báo:” tin nhắn/ảnh/video/file đã bị thu hồi”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Client có thể thu hồi tin nhắn, hình ảnh, video và file, </t>
+  </si>
+  <si>
+    <t>Đúng như mong đợi, chỉ có người gửi mới có thể thu hồi, người nhận không thể thu hồi</t>
+  </si>
+  <si>
+    <t>TC_16</t>
+  </si>
+  <si>
+    <t>Chức năng đăng xuất</t>
+  </si>
+  <si>
+    <t>Nhấn vào ô tài khoản để đăng xuất</t>
+  </si>
+  <si>
+    <t>Nhấn đăng xuất sẽ hiện Client để đăng nhập lại bằng tài khoản khác</t>
+  </si>
+  <si>
+    <t>Client sau khi đăng xuất thì sẽ bị tắt hoàn toàn</t>
+  </si>
+  <si>
+    <t>TC_17</t>
+  </si>
+  <si>
+    <t>Chức năng đăng ký</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sau khi mở lại sẽ hiện bảng đăng nhập, đăng ký và quên mật khẩu, nhấn vào ô đăng kí để điền Username, mật khẩu và tên hiển thị </t>
+  </si>
+  <si>
+    <t>username: Thử Nghiệm
+mật khẩu: thunghiem123
+tên hiển thị: thử nghiệm</t>
+  </si>
+  <si>
+    <t>Sau khi nhấn đăng kí thì sẽ có thêm tài khoản tên thử nghiệm hiện trong danh sách user</t>
+  </si>
+  <si>
+    <t>ImageTC-17
+Kết quả ImageTC-17</t>
+  </si>
+  <si>
+    <t>TC_18</t>
+  </si>
+  <si>
+    <t>Chức năng quên mật khẩu</t>
+  </si>
+  <si>
+    <t>Nhấn quên mật khẩu để lấy lại tài khoản quên mật khẩu.
+Nhập username đã quên mật khẩu, nhấn vào ô lấy mã để nhập mã reset rồi sau đó nhập mật khẩu mới</t>
+  </si>
+  <si>
+    <t>username: Thử Nghiệm
+Mã reset: (mã này thay đổi liên tục và ngẫu nhiên )
+Mật khẩu mới:thunghiem50</t>
+  </si>
+  <si>
+    <t>Sau khi nhập đúng mã reset và đặt mật khẩu mới thì sẽ hiện thông báo:"Đổi mật khẩu thành công", sau đó đăng nhập lại với mật khẩu mới để vô phần nhắn tin</t>
+  </si>
+  <si>
+    <t>ImageTC-18+1
+Kết quả ImageTC-18+1
+ImageTC-18+2
+Kết quả ImageTC-18+2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -206,6 +448,24 @@
       <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -277,33 +537,65 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="2"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="5"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -636,231 +928,578 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.109375" style="8"/>
-    <col min="2" max="2" width="11" style="8"/>
-    <col min="3" max="3" width="15.77734375" style="8"/>
-    <col min="4" max="4" width="16.44140625" style="8"/>
-    <col min="5" max="5" width="17.109375" style="8"/>
-    <col min="6" max="6" width="14.44140625" style="8"/>
-    <col min="7" max="7" width="10.33203125" style="8"/>
-    <col min="8" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="7.109375" style="2"/>
+    <col min="2" max="2" width="26" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="21.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="2"/>
+    <col min="9" max="9" width="8.88671875" style="1"/>
+    <col min="10" max="10" width="21.109375" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="J1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="151.80000000000001" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="13"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="4"/>
+    </row>
+    <row r="3" spans="1:11" ht="220.8" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="1:7" ht="234.6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="F3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="4"/>
+    </row>
+    <row r="4" spans="1:11" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" spans="1:7" ht="124.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="E4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="G4" s="13"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" spans="1:11" ht="69" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" spans="1:7" ht="69" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="G5" s="13"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+    </row>
+    <row r="6" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="5"/>
-    </row>
-    <row r="6" spans="1:7" ht="82.8" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="F6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="13"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="4"/>
+    </row>
+    <row r="7" spans="1:11" ht="69" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:7" ht="69" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="F7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="13"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" ht="69" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="B8" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="13"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" spans="1:11" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="B9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="5"/>
-    </row>
-    <row r="8" spans="1:7" ht="96.6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:7" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:11" ht="70.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" spans="1:11" ht="58.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="E11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="13"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" ht="118.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="13"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:11" ht="67.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="K13" s="16"/>
+    </row>
+    <row r="14" spans="1:11" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="18"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="K14" s="16"/>
+    </row>
+    <row r="15" spans="1:11" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="18"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="K15" s="16"/>
+    </row>
+    <row r="16" spans="1:11" ht="76.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="18"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+    </row>
+    <row r="17" spans="1:11" ht="55.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" s="18"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+    </row>
+    <row r="18" spans="1:11" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="18"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="K18" s="16"/>
+    </row>
+    <row r="19" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="18"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="K19" s="16"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J4" r:id="rId1" xr:uid="{5948687F-5235-4C94-B690-0DC336279BA8}"/>
+    <hyperlink ref="J6" r:id="rId2" xr:uid="{357784ED-03BA-48CB-A0E8-094DA2F96A04}"/>
+    <hyperlink ref="J7" r:id="rId3" xr:uid="{9B2DD5E7-BECF-424E-A92A-7BD32D6ABFCD}"/>
+    <hyperlink ref="J8" r:id="rId4" xr:uid="{A67FC0FE-3B01-4960-820B-6B72C7CE3EE1}"/>
+    <hyperlink ref="J12" r:id="rId5" xr:uid="{F2730E77-2212-4681-9F73-C4C0A739E663}"/>
+    <hyperlink ref="J14" r:id="rId6" xr:uid="{DAE379E1-CC8D-4407-B295-2006C3968641}"/>
+    <hyperlink ref="J15" r:id="rId7" xr:uid="{BD6E9BFA-15C4-4CDB-B8B1-4DCF4A455B17}"/>
+  </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
--- a/Extra/testcase.xlsx
+++ b/Extra/testcase.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hoctap\Lập Trình Mạng\Ung-Dung-ChatTCP\Extra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F153401C-0A61-4EC2-BD69-3520C266BAC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9BCC649-92E3-4A89-972E-2A45F482B6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="125">
   <si>
     <t>STT(Mã TC)</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>Kết quả mong đợi(Expected result)</t>
-  </si>
-  <si>
-    <t>Trạng thái(Status)</t>
   </si>
   <si>
     <t>TC_01</t>
@@ -422,6 +419,25 @@
 Kết quả ImageTC-18+1
 ImageTC-18+2
 Kết quả ImageTC-18+2</t>
+  </si>
+  <si>
+    <t>Trạng thái 1(Status)</t>
+  </si>
+  <si>
+    <t>Trạng thái 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client chạy song song với Server thì Port chỉ nhận số 5000, nếu nhập số khác 5000 và nhập chữ thì sẽ hiện thông báo:"không thể kết nối tới Server </t>
+  </si>
+  <si>
+    <t>Sau khi nhận tin nhắn mà chưa đọc thì khi tải lại lịch sử sẽ hiện lên tổng tin nhắn đã nhận bao gồm tin nhắn cũ và mới</t>
+  </si>
+  <si>
+    <t>Sau khi nhấn đăng xuất thì sẽ quay lại Client đăng nhập để truy cập vào tài khoản</t>
+  </si>
+  <si>
+    <t>ImageTC-16
+Kết quả ImageTC-16</t>
   </si>
 </sst>
 </file>
@@ -476,7 +492,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -536,18 +552,81 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -557,33 +636,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -592,13 +644,436 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="13">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -609,6 +1084,26 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4EF12B6-01F3-4FF6-8086-2D3505551CD1}" name="Table1" displayName="Table1" ref="A1:K20" totalsRowShown="0" headerRowBorderDxfId="11" tableBorderDxfId="12">
+  <autoFilter ref="A1:K20" xr:uid="{C4EF12B6-01F3-4FF6-8086-2D3505551CD1}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{407C634F-38BB-4D5D-9759-A22BBD583538}" name="STT(Mã TC)" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{1EBF301C-9DE5-452C-89AE-63AB3CE65E32}" name="Chức năng cần test" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{03379C37-9C01-431D-A3E0-A8B971C4BB14}" name="Các bước thực hiện(Steps)" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{2DB51D45-B1C7-42CE-9119-C1E5AB63EDE8}" name="Dữ liệu nhập vào(Test Data)" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{E50E6BD6-D1D4-43C1-ADB7-3CE2ED80FE38}" name="Kết quả mong đợi(Expected result)" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{EE302A62-431E-4E85-8EE6-BC4A1F60B45D}" name="Test1" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{AF489F94-995E-4928-BF96-0D915FCB5BB9}" name="Test2" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{171F06EA-4E90-4D7A-87FB-B1EFBDE98621}" name="Test 3" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{6D6445E0-5FA8-492F-B9CD-123B33DF2171}" name="Trạng thái 1(Status)" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{95887B5A-2564-4A33-BE00-9933053326C5}" name="Trạng thái 2" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{20C69844-8620-4CC8-919A-69588876071C}" name="Proof" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -931,575 +1426,606 @@
   <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.109375" style="2"/>
+    <col min="1" max="1" width="13.88671875" style="2" customWidth="1"/>
     <col min="2" max="2" width="26" style="2" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="27.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="33" style="2" customWidth="1"/>
     <col min="6" max="6" width="21.33203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" style="26" customWidth="1"/>
     <col min="8" max="8" width="8.88671875" style="2"/>
-    <col min="9" max="9" width="8.88671875" style="1"/>
-    <col min="10" max="10" width="21.109375" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="9" max="9" width="20.109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" customWidth="1"/>
+    <col min="11" max="11" width="21.109375" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="K1" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:11" ht="69" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="4"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="6"/>
+      <c r="K2" s="11" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="5" t="s">
+    <row r="3" spans="1:11" ht="138" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="B3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" s="4"/>
+      <c r="K3" s="12" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" ht="220.8" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="5" t="s">
+    <row r="4" spans="1:11" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J3" s="15" t="s">
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="4"/>
+      <c r="F4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="8"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="6"/>
+      <c r="K4" s="13" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" ht="124.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="5" t="s">
+    <row r="5" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="13"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" s="7" t="s">
+      <c r="B5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="6"/>
+      <c r="K5" s="10"/>
+    </row>
+    <row r="6" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11" ht="69" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="5" t="s">
+    <row r="7" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="6"/>
+      <c r="K7" s="13" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="K6" s="4"/>
+    <row r="8" spans="1:11" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="6"/>
+      <c r="K8" s="13" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="7" spans="1:11" ht="69" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="K7" s="4"/>
-    </row>
-    <row r="8" spans="1:11" ht="69" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+    <row r="9" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K8" s="4"/>
-    </row>
-    <row r="9" spans="1:11" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="B9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
+      <c r="C9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:11" ht="70.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J10" s="16" t="s">
+      <c r="F10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="8"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="6"/>
+      <c r="K10" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="124.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="K10" s="4"/>
-    </row>
-    <row r="11" spans="1:11" ht="58.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="B11" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="4"/>
+      <c r="E11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
+      <c r="G11" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="H11" s="4"/>
+      <c r="I11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:11" ht="118.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="8"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="6"/>
+      <c r="K12" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="K12" s="4"/>
     </row>
     <row r="13" spans="1:11" ht="67.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="D13" s="7"/>
+      <c r="E13" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17" t="s">
+      <c r="F13" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="8"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="6"/>
+      <c r="K13" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="G13" s="18"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="K13" s="16"/>
     </row>
     <row r="14" spans="1:11" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="C14" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="D14" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="E14" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="F14" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="G14" s="8"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="18"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="K14" s="16"/>
     </row>
     <row r="15" spans="1:11" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="C15" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="D15" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="E15" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="F15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" s="6"/>
+      <c r="K15" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="18"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="K15" s="16"/>
     </row>
     <row r="16" spans="1:11" ht="76.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="C16" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="D16" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="E16" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E16" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="18"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
+      <c r="F16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="8"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="6"/>
+      <c r="K16" s="14"/>
     </row>
-    <row r="17" spans="1:11" ht="55.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="17" spans="1:11" ht="85.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="C17" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="D17" s="7"/>
+      <c r="E17" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17" t="s">
+      <c r="F17" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="F17" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="G17" s="18"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
+      <c r="G17" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17" s="7"/>
+      <c r="I17" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="18" spans="1:11" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="C18" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="D18" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="E18" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="F18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="8"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="6"/>
+      <c r="K18" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="18"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="J18" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="K18" s="16"/>
     </row>
     <row r="19" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="C19" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="D19" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="E19" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="F19" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" s="8"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="6"/>
+      <c r="K19" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="18"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="J19" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="K19" s="16"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="22"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:K20">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="J4" r:id="rId1" xr:uid="{5948687F-5235-4C94-B690-0DC336279BA8}"/>
-    <hyperlink ref="J6" r:id="rId2" xr:uid="{357784ED-03BA-48CB-A0E8-094DA2F96A04}"/>
-    <hyperlink ref="J7" r:id="rId3" xr:uid="{9B2DD5E7-BECF-424E-A92A-7BD32D6ABFCD}"/>
-    <hyperlink ref="J8" r:id="rId4" xr:uid="{A67FC0FE-3B01-4960-820B-6B72C7CE3EE1}"/>
-    <hyperlink ref="J12" r:id="rId5" xr:uid="{F2730E77-2212-4681-9F73-C4C0A739E663}"/>
-    <hyperlink ref="J14" r:id="rId6" xr:uid="{DAE379E1-CC8D-4407-B295-2006C3968641}"/>
-    <hyperlink ref="J15" r:id="rId7" xr:uid="{BD6E9BFA-15C4-4CDB-B8B1-4DCF4A455B17}"/>
+    <hyperlink ref="K15" r:id="rId1" xr:uid="{BD6E9BFA-15C4-4CDB-B8B1-4DCF4A455B17}"/>
+    <hyperlink ref="K14" r:id="rId2" xr:uid="{DAE379E1-CC8D-4407-B295-2006C3968641}"/>
+    <hyperlink ref="K12" r:id="rId3" xr:uid="{F2730E77-2212-4681-9F73-C4C0A739E663}"/>
+    <hyperlink ref="K8" r:id="rId4" xr:uid="{A67FC0FE-3B01-4960-820B-6B72C7CE3EE1}"/>
+    <hyperlink ref="K7" r:id="rId5" xr:uid="{9B2DD5E7-BECF-424E-A92A-7BD32D6ABFCD}"/>
+    <hyperlink ref="K6" r:id="rId6" xr:uid="{357784ED-03BA-48CB-A0E8-094DA2F96A04}"/>
+    <hyperlink ref="K4" r:id="rId7" xr:uid="{5948687F-5235-4C94-B690-0DC336279BA8}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId8"/>
+  <tableParts count="1">
+    <tablePart r:id="rId9"/>
+  </tableParts>
 </worksheet>
 </file>